--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="7">
@@ -88,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -115,6 +119,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -568,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -578,6 +594,7 @@
     <col width="66" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -616,6 +633,11 @@
           <t>Priority</t>
         </is>
       </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Founder ruling 2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -653,6 +675,11 @@
           <t>P0 — a number that is not what it says it is</t>
         </is>
       </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>SETTLED — the target is now the person's OWN typed number ('What's your target nest egg?'), so it owes nobody 80%. What survives: the app's SUGGESTION, offered when the field is blank, still rounds itself under its own line and must be fixed (round up, not to nearest).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -690,6 +717,11 @@
           <t>P0 — same class as D1, and it is the sentence you built the screen around</t>
         </is>
       </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>STANDS — same rounding class. 'Raises your odds to 80%' must actually deliver 80%.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -727,6 +759,11 @@
           <t>P0 — the founder's own reason for killing the second gauge applies here</t>
         </is>
       </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>DISSOLVES — with a typed target the gap and the saving are measured against the SAME number, so they become one arithmetic. NOTE: the Short row is not in the design file; I introduced it when the second gauge was replaced with dollar lines. The design showed '$909,152 of $1.9M target' and never printed the gap in dollars.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -764,6 +801,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>RESHAPED — with a typed target, 'more than you need' is simply true when you pass your own target.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -801,6 +843,11 @@
           <t>P1 — and it contradicts the note under it, 'the same paycheck as Home's card'</t>
         </is>
       </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — awaiting your call</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -838,6 +885,11 @@
           <t>P1 — worst possible moment for an empty box</t>
         </is>
       </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — awaiting your call</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -875,6 +927,11 @@
           <t>P1 — a built screen is now unreachable</t>
         </is>
       </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — awaiting your call</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -912,6 +969,11 @@
           <t>P1 — a decision that was adopted and then not built</t>
         </is>
       </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — awaiting your call</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -949,6 +1011,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — awaiting your call</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -986,6 +1053,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — awaiting your call</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1023,6 +1095,11 @@
           <t>P1 — the one distinction the whole screen turns on</t>
         </is>
       </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — awaiting your call</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1060,6 +1137,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — awaiting your call</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1095,6 +1177,95 @@
       <c r="G14" s="7" t="inlineStr">
         <is>
           <t>P2</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — awaiting your call</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>The retirement parameters read as parameters, not questions</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Your age · Monthly spending in retirement · WHAT COUNTS TOWARD RETIREMENT · BIG ONE-TIME COSTS · Retire at · Plan to age · Extra saving each month — all statements, none of them a question a person can answer out loud.</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Measured on the built tab. The same parameters are also asked on the Retirement cockpit, What-drives-this and What-if-I-save-more — four surfaces, so a Plan-tab-only change would make them disagree.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Mocked: mockups/Plan-redesign-Aug-12/plan-questions-and-typed-target-v1-2026-08-12.html — sweep all four surfaces in one change.</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>P1 — founder ruling 2026-08-12</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>RULED — mock awaiting approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>There is no field for the person's own target nest egg</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>The app works the target out and never asks. The founder's model is the opposite: you type your target and the app measures you against it.</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>No such field exists anywhere in the app (searched the whole source).</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Add 'What's your target nest egg?' as a fact, marked YOURS; keep the app's 80%-odds figure as the suggestion when it is left blank. Same mock.</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>P1 — founder ruling 2026-08-12</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>RULED — mock awaiting approval</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -42,7 +42,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00F3F3F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EDDD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -92,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -131,6 +136,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -640,86 +654,86 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>The number</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>The 'Target nest egg' is not the number that gives you 80% odds</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>The row is defined as the pot that reaches 80% odds. Pat's screen prints $1,370,000. Reaching exactly that pot the way Pat actually reaches it — saving from 58, through the market — gives 49% odds, not 80%. Even the target's own model (a plan starting the day you retire, holding that balance) returns 76%.</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Ran the simulation: planTarget() → target $1,370,000; simulate() with that balance = 76% in its own model, 49% in the real plan. src/domain/planning/target.ts:49</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>Two causes. (a) the bisection result is rounded to the NEAREST $10,000, so it can round below the threshold it just solved for — round UP instead. (b) the target is solved in a different model from the odds it is printed beside; either solve it in the same model, or label it as what it is.</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>P0 — a number that is not what it says it is</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>SETTLED — the target is now the person's OWN typed number ('What's your target nest egg?'), so it owes nobody 80%. What survives: the app's SUGGESTION, offered when the field is blank, still rounds itself under its own line and must be fixed (round up, not to nearest).</t>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — founder: 'round up'. targetAtRetirement now rounds UP to the next $10,000. Measured before/after on Pat: target $1,370,000 delivering 76% → target $1,380,000 delivering 81%. Pinned by src/domain/planning/target_rounding.test.ts (the promise, not the implementation: holding the target must deliver ≥80%, and one step lower must miss, so it cannot be inflated to pass).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>The number</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>'raises your odds to 80%' actually raises them to 79%</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>The bridge sentence promises 80%. The saving it names ($53,000/yr for Pat) produces 79% when you run it.</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>simulate() with annual_contribution = requiredExtraAnnual → 79. Same rounding class as D1: Math.round(found/500)*500 in requiredAnnualSaving(). src/domain/planning/target.ts:58</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Round the solved saving UP to the next $500, not to the nearest. One-line fix; same fix as D1's (a).</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>P0 — same class as D1, and it is the sentence you built the screen around</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>STANDS — same rounding class. 'Raises your odds to 80%' must actually deliver 80%.</t>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — same ruling, same one-word change. requiredAnnualSaving rounds UP to the next $500. Before: $53,000 delivering 79%. After: $53,500 delivering 81%. Same pin file.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -42,7 +42,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +79,11 @@
         <fgColor rgb="00D6EDDD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE9F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -97,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -145,6 +150,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -780,44 +794,44 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>The number</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Mid-change: 'more than you need' is hidden, but the ask stays on screen</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>Raise the retire age by one and the screen shows On track for $1,461,096 against a Target of $1,400,000 — above target — then still says 'Adding $53,300 a year closes it'. The gap row correctly stands down; the sentence does not.</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>Measured on the mid-change render (one press of Raise Retire at, one of Raise Extra saving).</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>When the projected pot clears the target but the odds have not, say that in one sentence instead of asking for money with no gap shown.</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>RESHAPED — with a typed target, 'more than you need' is simply true when you pass your own target.</t>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>CLOSED INTO THE REDESIGN 2026-08-13 — founder approved the recommendation. The suppression rule that caused it dies with the typed target. TWO THINGS IT LEFT BEHIND, both now in brief v3: (1) the closing sentence comes BACK under the shortfall, measured against THEIR target — 'Saving $84,500 a year over your 7 years to 65 reaches your target'. The v3 handoff had dropped it, leaving the hero stating a gap and offering nothing. It must be SOLVED not formula'd: the closed-form annuity gives $82,000 and lands $22,000 SHORT of the target it promises — the same class as D1/D2. (2) NEW REQUIRED STATE: already past your own target, undrawn anywhere. Not rare — type $800,000 and Pat is at 114% of target with 45% odds. Plus the mirror: a $1,500,000 target is reached by saving $24,000/yr at 64% odds, so someone can hit their number exactly and still not be at 80%. Neither may look like an error.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -836,44 +836,44 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>The retirement paycheck rows have no names</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>June's paycheck reads $2,600 / $1,400 / = Guaranteed $4,000 — the words 'Social Security' and 'Pension' are simply absent. The mock names every row.</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>PlanHubScreen.tsx:243 renders {g.label}; the engine's field is `source`. Home's PaycheckCard (line 47), MonthDetail (72) and PaycheckMonths (44) all use g.source — the Plan tab is the only one of the four that is wrong.</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Use g.source. One word. The class was checked: 1 of 4 consumers was broken.</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>P1 — and it contradicts the note under it, 'the same paycheck as Home's card'</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — awaiting your call</t>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — founder: 'fix it'. PlanHubScreen read g.label off each guaranteed-income row; the engine's field is g.source, which is what Home's PaycheckCard, MonthDetail and PaycheckMonths all read. One word. Class re-checked: 3 of 4 consumers were always correct, so nothing else to sweep. PINNED by src/__tests__/paycheck_row_names.test.tsx — three tests: the Plan tab names every row, it names them the same way Home does (the note under it claims one set of numbers), and a source GUARD so no screen reaches for .label again. VERIFIED THE PIN BITES: reverted the fix and 2 of the 3 failed, restored and all passed — the Home comparison passes either way, correctly, because Home was never broken.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -878,44 +878,44 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>The impossible state can say 'here's what actually moves it' and then show nothing</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>The levers list drops any lever worth 0 points. For someone deep enough in trouble, all of them are worth 0 — the band 'WHAT ACTUALLY MOVES IT' then renders with no rows under a sentence that just promised them.</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>Ran it: age 64, $20,000 saved, $9,000/mo spending → impossible = true, lever count = 0.</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>When nothing moves it, say so honestly in a sentence — that is the one screen state where a dead end is unforgivable.</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>P1 — worst possible moment for an empty box</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — awaiting your call</t>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>RULED 2026-08-13, MOCKED, NOT YET BUILT. Founder: 'if the odds are zero — don't show zero', then chose option ONE: the zero never appears anywhere. Order of what we say, founder-approved: THE HONEST SENTENCE FIRST, FREE ROUTES SECOND, A FEE-ONLY HOURLY PLANNER THIRD. Scope is FOUR surfaces, not one — oddsLine() is a single shared helper printed by Plan, Home, Net worth and the spoken label, so a Plan-only fix would leave Home greeting the person with a bare 0%. WHAT RUNNING IT CHANGED: 'no single lever helps' was true only because our levers are too timid (they test +2 years and −$400/mo). Measured on the example — 64, $20,000 saved, $9,000/mo, SS $2,400 from 67 — retiring at 65 gives 0% at EVERY spending level down to $2,200, because the two years before Social Security starts drain the pot; retire at 67 and $2,400/mo gives 100%, and the most they can spend from 67 is ~$2,450. So the app knows a specific, useful, true sentence and was showing an empty box instead. Mock: mockups/Plan-redesign-Aug-12/low-odds-honest-sentence-v1-2026-08-13.html (Plan + Home + Net worth, every figure sourced). FLOOR PROPOSED at under 5% — zero is the obvious trigger but 1% and 3% are equally useless to read; founder to confirm. NEW ENGINE WORK: the earliest age that works and the spending level that works from it — neither exists. FLAGGED: this is the one place the app replaces a true number with prose, and it should be a decision made on purpose.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -920,44 +920,44 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>There is no way to add a big one-time cost from the Plan tab</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>The tab shows BIG ONE-TIME COSTS and warns that leaving them out means 'the plan quietly assumes the roof never needs doing' — and offers no way to add one. The mock draws the door: '+ Add a big cost — leaving them out assumes it never happens'.</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>/big-costs still exists and is still routed, but nothing in the app links to it any more (grep: only the route guard, the screen itself and its test). The rebuild dropped the door.</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Put the mock's add row back at the foot of the section.</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>P1 — a built screen is now unreachable</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — awaiting your call</t>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — founder: 'yes to both'. (1) THE DOOR IS BACK: '＋ Add a big cost ›' at the foot of the BIG ONE-TIME COSTS section in PlanInputs, routing to /big-costs — the same row Claude Design's v3 draws, so it converges with the redesign rather than being thrown away. Root cause owned: on 2026-08-12 I moved three things off the Plan tab and the commit said all three landed in section 1; two did, this one did not, leaving a fully built screen reachable from NOWHERE (not a screen, not the menu). (2) THE CLASS IS NOW GUARDED: NEW src/__tests__/orphan_route_guard.test.ts — every registered route must have an inbound link from somewhere a person could tap. The forward direction was already guarded (no button may point at a route that does not exist); the reverse had nothing. VERIFIED IT BITES: removing the door turns it red and names /big-costs. MY FIRST VERSION OF THE GUARD WAS WRONG — it scanned only screens and components and reported 7 orphans, 3 of them false: /contribution-room, /worth-a-look and /idle-cash are all reached from INSIGHT CARDS, which carry their own route and live in src/domain, and /savings is reached from the onboarding summary. Now scans the whole of src. A guard that looks in too few places is worse than none — it cries wolf and gets muted. The three genuine orphans (/income, /invest, /income-detail) are recorded by NAME in the guard with the founder's 2026-08-02 'keep ALL orphans' ruling and the reason (future age groups), so deleting one stays a founder call rather than a tidy-up. Gates: 1623 green, tsc clean, UI gate passed. STILL OPEN: whether big costs also gets a ☰ menu entry as a second way in.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -962,44 +962,44 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>D8</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>The number</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>A retiree is shown a 'Target nest egg' and two different 'to spare' figures</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>June's screen shows Target nest egg $380,000 · More than you need $1,251,000, and four lines later '~$5,354,000 to spare'. Two spare numbers, one screen. The handoff review adopted the opposite: the paycheck REPLACES the target framing for someone already drawing down.</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Measured on June's render. PlanOutcome renders the target block whenever a target exists, with no lens check (PlanOutcome.tsx:62).</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Skip the target block for the retired lens — the paycheck card is the retiree's version of it, as agreed.</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>P1 — a decision that was adopted and then not built</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — awaiting your call</t>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — founder: 'fix it now'. The target block, the shortfall/more-than-you-need row and both target-reaching bridge sentences now stand down for the RETIRED lens (PlanOutcome). A target is a 'will I get there' framing; once someone is drawing down the question is 'is this covering me', which the paycheck answers — adopted when the design handoff arrived, reconfirmed 2026-08-13 when the founder chose the paycheck for June's second dial, and never built until now. BEFORE (measured on June's corrected $985,000): 'On track for $985,000 · Target nest egg $400,000 · More than you need $585,000 · You've cleared the 80% mark — nothing more to put away to stay there' AND four lines later '~$2,336,000 to spare' — two spare figures measuring different things (today's money vs a target pot; the median left at 94), neither labelled as which. AFTER: the odds, then one spare figure on the line that also carries her withdrawal rate. Also removed for retirees: 'nothing more to put away to stay there', said to someone no longer paying into anything. The impossible-state levers block is KEPT for retirees — spending less and claiming later still move a retiree's odds. PINNED src/components/__tests__/PlanOutcome.retired.test.tsx (5 tests, including one that someone still working is unaffected). Converges with the redesign: June's frames in the v3 handoff carry no target rows either. Gates: 1628 green, tsc clean, UI gate passed.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -1004,44 +1004,44 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>D9</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Appearance</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Seven filled green bands where the mock draws three</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>The mock has two heading levels: a quiet deep-green label on the page (YOUR RETIREMENT PLAN, FACTS, CHOICES, DECISIONS) and a filled green band (WILL MY MONEY LAST?, WHAT COUNTS, BIG ONE-TIME COSTS). The build makes all seven filled bands, so the page reads as one striped block with no hierarchy.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Measured: 7 views with background #085041 on Pat's render. Mock CSS: .pl-sec = plain text, .pl-banner = filled.</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Use the band for the three the mock bands, and a quiet label for the other four.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — awaiting your call</t>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — founder: 'I am good with plan v3', adopting the Claude Design v3 heading hierarchy. Root cause was never a Plan bug: the app had exactly ONE heading style (the shared band adopted 2026-08-04, used in 35 files), and the Plan tab has seven things needing a name, so every one became a full-width green bar. SectionBand gains a `quiet` level — deep-green caps on the page, no fill. THE RULE: a filled band is reserved for a group that carries its own TOTAL riding the right edge; a section title is a quiet label. MEASURED: 7 filled bands -&gt; 2, and the two that remain (WHAT COUNTS TOWARD RETIREMENT $909,152, BIG ONE-TIME COSTS $18,000) are exactly the ones with totals. DEVIATION FROM v3, deliberate: the note specifies the quiet label in the mid brand green #178F6B, which measures 3.78:1 on the app background and FAILS the 4.5:1 small-text floor (my own review blocker B6). Built in #085041, which measures 8.74:1 — the same lesson the filled band already carries in the theme file. PINNED: every filled band must contain a money figure, at most 3 may exist, and the quiet label must be the accessible green at 11px. PLAN ONLY — the prop is optional and defaults off, so Net worth and the other 34 files are untouched by construction. Net worth would not change anyway: its bands are genuine section headers with totals, which is what the filled band is FOR under the new rule. Gates: 1631 green, tsc clean, UI gate passed.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -1046,44 +1046,44 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>D10</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Appearance</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>The two top bands are different widths</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>'YOUR RETIREMENT PLAN' bleeds to the card edge; 'WILL MY MONEY LAST?' directly beneath it is inset 12pt on each side. Two green bars, stacked, not aligned.</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Measured: marginHorizontal −12 on the first, 0 on the second.</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>One or the other — pass inCard to both, or neither.</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — awaiting your call</t>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — founder: 'Since we are going to label this tab Retire under Plan (parent tab). We can drop your retirement plan heading.' TWO PARTS. (1) THE HEADING IS GONE: 'YOUR RETIREMENT PLAN' sat directly above 'WILL MY MONEY LAST?' saying nearly the same thing — the heavy green bars disguised the repetition until the D9 hierarchy change made both quiet labels and it became plain. The tab will be named Retire under Plan, so the card no longer announces which tab it is on; the question IS the heading. (2) THE ALIGNMENT FIX WENT DEEPER THAN THE FINDING SAID. My first attempt made the quiet label IGNORE `inCard` — and measuring showed that only moved the problem: headings outside a card then sat 12pt LEFT of the ones inside, and 'DECISIONS YOU CAN MAKE TODAY' was the one out of line. The flag actually carries the fact that matters — whether a card's own padding already sits to the left — so the quiet label now adds ONE inset inside a card and TWO outside, landing every heading on the same line as every row. Every quiet band was audited for which side of that it is on. MEASURED BEFORE/AFTER: six headings at [24, 12] -&gt; all six at 24. PINNED: all section headings share one left edge (a set of insets with length 1, so a new heading cannot drift), and the dropped heading is pinned absent. STALE PIN UPDATED, not deleted: plan_hub_v9 asserted the old heading was present — now asserts it is absent, with the ruling recorded beside it. Gates: 1638 green, tsc clean, UI gate passed.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -1088,44 +1088,44 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>D11</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Appearance</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>FACT and DRAFT chips are two nearly identical greens</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>The chips are the design's main device for telling a saved fact from a draft choice — adopted as drawn. Built, FACT is grey text on #DFF2E9 and DRAFT is green text on #E1F5EE: two light greens two shades apart. In the mock the FACT tag is neutral grey and only DRAFT is green.</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Measured on the render. They are also plain highlighted words — no rounded pill, spacing faked with spaces — because a nested Text cannot take padding reliably.</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Put FACT back on the neutral grey token, and give the chips a real pill (a small View, not a nested Text).</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>P1 — the one distinction the whole screen turns on</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — awaiting your call</t>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — founder: 'do it'. The FACT badge moves off the light GREEN band tint onto the NEUTRAL tint, so a saved answer reads quiet and grey while something being tried on reads green. Claude Design had specified this correctly and the build got it wrong — their note: 'FACT tag: neutral chip… this colour distinction is the primary way a person tells facts from choices at a glance.' It matters more than a badge usually would: FACT vs DRAFT is the entire facts-save / choices-commit model, and with both badges two shades of one green a person had to STOP AND READ the word to learn whether their answer was already saved — which is the one job a badge exists to spare them. PINNED two ways: the three chips must sit on different colour families (FACT explicitly on the neutral tint, explicitly NOT on the green band tint it used to wear), and the quiet chip's contrast is RECOMPUTED in the test from the live tokens, so a future token change that drops it under the 4.5:1 small-text floor fails instead of shipping (it measures 4.60:1). DEFERRED BY AGREEMENT: the badges are not real pills — they are words with a background, their inset faked with blank spaces, because a nested Text cannot take padding reliably in React Native. It looks passable at default text size and drifts apart when a reader turns their type up, which this audience does. Left to Claude Design's redraw rather than patched. LESSON: the colour-token guard caught raw hex codes I had put in a CODE COMMENT explaining the contrast — the guard cannot tell a comment from a style, and it was right to fail; the measurement lives in the test now. Gates: 1640 green, tsc clean, UI gate passed.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -1130,44 +1130,44 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>The tax-advantaged-room sentence can never appear</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>The mock's bridge sentence ends '$32,500/yr of it fits in tax-advantaged room.' The code for it exists and is correct — but the value feeding it is hard-coded to undefined, so the sentence never renders.</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>PlanHubScreen.tsx:84 — `const roomAnnual = undefined;`</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Feed it the contribution-room figure the app already computes, or delete the dead branch and drop the line from the spec.</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — awaiting your call</t>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — founder approved the hedged wording. The sentence is wired and now reads 'About $32,500 of that should fit in tax-advantaged room, going by the $800 a month you told us you already put in.' The figure is NOT new: the same headroom already drove Home's 401(k) insight and the contribution-room screen — the Plan sentence existed and its value was hard-coded undefined, so nobody had ever seen it. FOUNDER'S QUESTION CHANGED THE WORDING: 'How do we know person has not already taken advantage of 401K contributions?' Checked — k401Headroom takes the IRS limit minus what they TOLD US they contribute monthly, times twelve. So it does subtract contributions, but it assumes that figure held evenly all year, which is wrong for anyone who front-loaded, started or stopped mid-year, changed job, or defers a bonus, and it sees no employer match. We never read a payroll or plan statement — there is no source of truth for 'how much has actually gone in this year'. Over-contributing to a 401(k) carries a real tax penalty, so an estimate presented as a fact about someone's allowance is not acceptable. CLASS FIXED, NOT THE INSTANCE — the same unhedged claim was live in TWO other places and both are corrected: Home's insight ('You can still contribute $32,500 this year' → 'About $32,500 of this year's tax-advantaged room looks unused — an estimate from what you told us you contribute, not from your payroll') and the contribution-room screen ('You've put in $X of the $Y limit this year' → 'That is about $X of the $Y limit — worked out from what you told us you contribute each month, not from your payroll, so check it against your latest statement'). The sentence stays silent entirely when no contribution was ever given, rather than guessing. Retirees never see it. PINNED: the hedged wording, the named assumption, and the silent case. A stale pin asserting the old 'fits in tax-advantaged room' was updated to the new behaviour with the reason beside it. Gates: 1641 green, tsc clean, UI gate passed.</t>
         </is>
       </c>
     </row>

--- a/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
+++ b/mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx
@@ -1172,44 +1172,44 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Appearance</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>'What drives this? ›' is a 20pt tap target</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>A single line of text inside a touchable with no minimum height — roughly 20pt tall against the 44pt rule.</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Measured: no minHeight, no vertical padding, fontSize 15. The 44pt ratchet only covers Net worth and the money sheets, so nothing caught it.</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>Give it the 44pt minimum, and widen the ratchet to cover the Plan surface.</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>OPEN — awaiting your call</t>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>FIXED 2026-08-13 — founder: 'go'. 'What drives this? ›' was a single 15pt line inside a touchable with no height and no padding: about 19pt of target, against a 44pt rule that exists precisely for this audience. It now carries minHeight 44 and centres its text. THE OTHER FIVE flagged by the measurement were checked and are fine — the decision rows, the next-decision card and the Sharpen card all clear 44 once their own content is counted (58-62pt). PINNED with a check that counts a row's declared height, its minimum, or its padding plus its lines. THREE DEFECTS IN MY OWN CHECK, each found by trying to make it fail rather than trusting it: (1) it read only minHeight and padding, so the stepper buttons — declared a flat 44x44 via `height` — were reported as 19pt targets it had invented; (2) it required a style prop to be present, so a touchable with NO style at all was skipped entirely, which is exactly how a 19pt target comes about — the check walked past the defect it exists to find; (3) it sat outside the describe that seeds the persona, so it rendered the FIRST-DAY screen where this link does not exist, and passed without ever looking at the thing it was written to check. All three fixed, then VERIFIED BY REVERTING the fix: the pin now goes red naming 'What drives this? › ≈ 19pt'. STILL OPEN, app-wide, NOT part of this finding: the ⓘ info dot is a 13pt glyph with 6/4 padding — roughly 21pt — and has no hitSlop. It appears on most screens, so raising it is one change in one component but it needs a decision and a device check, since padding would alter layout and hitSlop on a Text is not reliably supported. Gates: 1642 green, tsc clean, UI gate passed.</t>
         </is>
       </c>
     </row>
